--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,64 +28,46 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>4 comensales, 45m, Dificultad baja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>piezas de pollo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Pollada con arroz</x:t>
+    <x:t>10 comensales, 4h, Merienda, Dificultad muy baja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bolsa de pan para torrijas (o pan de barra)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Torrijas al horno</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadas soperas de ají panca en pasta</x:t>
+    <x:t>litro de leche</x:t>
+  </x:si>
+  <x:si>
+    <x:t>piel de limón</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>canela en rama</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>cucharadas soperas de ajo molido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de comino molido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de pimienta negra molida</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de orégano seco molido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadas soperas de mostaza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mililitros de vinagre tinto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mililitros de sillao</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharaditas de sal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aceite c/n</x:t>
+    <x:t>cucharadas soperas de azúcar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huevos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>canela molida</x:t>
+  </x:si>
+  <x:si>
+    <x:t>azúcar para espolvorear</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -436,7 +418,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D12"/>
+  <x:dimension ref="A1:D9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -472,10 +454,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>8</x:v>
@@ -486,10 +468,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>8</x:v>
@@ -500,10 +482,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>8</x:v>
@@ -517,7 +499,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>8</x:v>
@@ -528,10 +510,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>8</x:v>
@@ -542,10 +524,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>8</x:v>
@@ -556,54 +538,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
-      <x:c r="A12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,46 +28,49 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>10 comensales, 4h, Merienda, Dificultad muy baja</x:t>
+    <x:t>4 comensales, 15m, Plato principal, Dificultad baja</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>bolsa de pan para torrijas (o pan de barra)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Torrijas al horno</x:t>
+    <x:t>chorro de aceite de oliva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Ensalada de gulas y gambas</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>litro de leche</x:t>
-  </x:si>
-  <x:si>
-    <x:t>piel de limón</x:t>
-  </x:si>
-  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>canela en rama</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadas soperas de azúcar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huevos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>canela molida</x:t>
-  </x:si>
-  <x:si>
-    <x:t>azúcar para espolvorear</x:t>
+    <x:t>guindillas secas de cayena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gramos de gambas peladas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gramos de gulas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lata de mejillones al natural (de unos 120 g)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gramos de canónigos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>granada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pizca de sal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -454,10 +457,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>8</x:v>
@@ -468,10 +471,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>8</x:v>
@@ -485,7 +488,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>8</x:v>
@@ -496,7 +499,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>14</x:v>
@@ -510,10 +513,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>8</x:v>
@@ -524,10 +527,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>8</x:v>
@@ -538,10 +541,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>8</x:v>

--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,49 +28,91 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>4 comensales, 15m, Plato principal, Dificultad baja</x:t>
+    <x:t>8 comensales, 45m, Plato principal, Dificultad baja</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>chorro de aceite de oliva</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Ensalada de gulas y gambas</x:t>
+    <x:t>Pollo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Arroz con pollo</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>kilogramo de Arroz blanco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cebolla</x:t>
+  </x:si>
+  <x:si>
+    <x:t>¼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ajoporro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pimentón rojo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pimentón verde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dientes de Ajo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zanahoria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lata de Guisantes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lata de Maíz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>½</x:t>
+  </x:si>
+  <x:si>
+    <x:t>taza de Aceite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharada sopera de Mostaza</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>guindillas secas de cayena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gramos de gambas peladas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gramos de gulas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lata de mejillones al natural (de unos 120 g)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gramos de canónigos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>granada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pizca de sal</x:t>
+    <x:t>cucharadas soperas de Salsa inglesa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharadita de Orégano en polvo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharadita de Comino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tazas de Agua                                                                    (2400 mililitros)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cubitos de caldo de pollo concentrado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharadita de Colorante alimentario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pizca de Sal y Pimienta</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -421,7 +463,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D9"/>
+  <x:dimension ref="A1:D21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -457,10 +499,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>8</x:v>
@@ -471,10 +513,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>8</x:v>
@@ -488,7 +530,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>8</x:v>
@@ -502,7 +544,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>8</x:v>
@@ -513,10 +555,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>8</x:v>
@@ -527,10 +569,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>8</x:v>
@@ -544,9 +586,177 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:4">
+      <x:c r="A13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:4">
+      <x:c r="A14" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:4">
+      <x:c r="A15" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:4">
+      <x:c r="A16" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:4">
+      <x:c r="A17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:4">
+      <x:c r="A18" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:4">
+      <x:c r="A19" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,91 +28,46 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>8 comensales, 45m, Plato principal, Dificultad baja</x:t>
+    <x:t>4 comensales, 45m, Postre, Dificultad baja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unidades de Huevos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Roscón de naranja</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>Pollo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Arroz con pollo</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>kilogramo de Arroz blanco</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cebolla</x:t>
-  </x:si>
-  <x:si>
-    <x:t>¼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ajoporro</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pimentón rojo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pimentón verde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dientes de Ajo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zanahoria</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lata de Guisantes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lata de Maíz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>½</x:t>
-  </x:si>
-  <x:si>
-    <x:t>taza de Aceite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharada sopera de Mostaza</x:t>
+    <x:t>sobre de Levadura Royal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unidad de Yogur natural o de limón</x:t>
+  </x:si>
+  <x:si>
+    <x:t>300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gramos de Harina (4 vasos del envase del yogur)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vaso de Yogur de aceite</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>cucharadas soperas de Salsa inglesa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de Orégano en polvo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de Comino</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tazas de Agua                                                                    (2400 mililitros)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cubitos de caldo de pollo concentrado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de Colorante alimentario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pizca de Sal y Pimienta</x:t>
+    <x:t>vasos de yogur de azúcar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unidad de Naranja o limón y su ralladura</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -463,7 +418,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D21"/>
+  <x:dimension ref="A1:D8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -499,10 +454,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>8</x:v>
@@ -513,10 +468,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>8</x:v>
@@ -527,10 +482,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>8</x:v>
@@ -541,10 +496,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>8</x:v>
@@ -555,10 +510,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>8</x:v>
@@ -569,194 +524,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
-      <x:c r="A12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:4">
-      <x:c r="A13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:4">
-      <x:c r="A14" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:4">
-      <x:c r="A15" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:4">
-      <x:c r="A16" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:4">
-      <x:c r="A17" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:4">
-      <x:c r="A18" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:4">
-      <x:c r="A19" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:4">
-      <x:c r="A20" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:4">
-      <x:c r="A21" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,46 +28,52 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>4 comensales, 45m, Postre, Dificultad baja</x:t>
+    <x:t>2 comensales, 45m, Dificultad baja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rebanadas de pan de pan duro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Sopa de ajo de la abuela</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huevos</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>unidades de Huevos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Roscón de naranja</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>dientes de ajos</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>sobre de Levadura Royal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>unidad de Yogur natural o de limón</x:t>
-  </x:si>
-  <x:si>
-    <x:t>300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gramos de Harina (4 vasos del envase del yogur)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>vaso de Yogur de aceite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>vasos de yogur de azúcar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>unidad de Naranja o limón y su ralladura</x:t>
+    <x:t>cucharada postre de pimentón dulce</x:t>
+  </x:si>
+  <x:si>
+    <x:t>litro de caldo o agua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gramos de jamón en taquitos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chorro de aceite de oliva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pizca de sal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -418,7 +424,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D8"/>
+  <x:dimension ref="A1:D9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -468,10 +474,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>8</x:v>
@@ -482,10 +488,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>8</x:v>
@@ -496,10 +502,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>8</x:v>
@@ -510,10 +516,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>8</x:v>
@@ -524,12 +530,26 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,52 +28,73 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>2 comensales, 45m, Dificultad baja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rebanadas de pan de pan duro</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Sopa de ajo de la abuela</x:t>
+    <x:t>4 comensales, 45m, Dificultad baja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>piezas de piernas y encuentro de pollo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Carapulcra de pollo</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cebolla</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dientes de ajo picado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharadas soperas de ají panca en pasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>¼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharadita de comino molido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cucharadita de pimienta negra molida</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rama de canela</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>huevos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dientes de ajos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharada postre de pimentón dulce</x:t>
-  </x:si>
-  <x:si>
-    <x:t>litro de caldo o agua</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gramos de jamón en taquitos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>chorro de aceite de oliva</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pizca de sal</x:t>
+    <x:t>hojas de laurel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sal al gusto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aceite c/n</x:t>
+  </x:si>
+  <x:si>
+    <x:t>puñado de maní molido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gramos de papa seca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>litros de caldo de pollo</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -424,7 +445,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D9"/>
+  <x:dimension ref="A1:D14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -502,10 +523,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>8</x:v>
@@ -516,7 +537,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -530,7 +551,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>18</x:v>
@@ -544,12 +565,82 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:4">
+      <x:c r="A13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:4">
+      <x:c r="A14" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="C14" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/RPA-EOI/excel/Receta.xlsx
+++ b/RPA-EOI/excel/Receta.xlsx
@@ -28,73 +28,28 @@
     <x:t>nombre</x:t>
   </x:si>
   <x:si>
-    <x:t>4 comensales, 45m, Dificultad baja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>piezas de piernas y encuentro de pollo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Receta de Carapulcra de pollo</x:t>
+    <x:t>3 comensales, 30m, Plato principal, Dificultad baja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pimientos rojos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Receta de Pimientos rellenos con huevo</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cebolla</x:t>
-  </x:si>
-  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>dientes de ajo picado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadas soperas de ají panca en pasta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>¼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de comino molido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cucharadita de pimienta negra molida</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rama de canela</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hojas de laurel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sal al gusto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aceite c/n</x:t>
-  </x:si>
-  <x:si>
-    <x:t>puñado de maní molido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gramos de papa seca</x:t>
-  </x:si>
-  <x:si>
-    <x:t>litros de caldo de pollo</x:t>
+    <x:t>huevos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>morcillas</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -445,7 +400,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D14"/>
+  <x:dimension ref="A1:D4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -495,152 +450,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
-      <x:c r="A8" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
-      <x:c r="A12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:4">
-      <x:c r="A13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:4">
-      <x:c r="A14" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
